--- a/data/mapas/Mapa_de_Carrera_Frances.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Frances.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B34, "SI")</f>
+        <f>COUNTIF(B6:B41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C34, "SI")</f>
+        <f>COUNTIF(C6:C41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F34, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Lengua Francesa I</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B34, "SI")/24</f>
+        <f>COUNTIF(B6:B41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Fonética y Fonología Francesa I</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C34, "SI")/24</f>
+        <f>COUNTIF(C6:C41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Disciplina</t>
+          <t>Gramática Francesa I</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente I</t>
+          <t>Práctica de Laboratorio y Expresión Oral I</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -831,10 +831,37 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Civilización y Cultura Francesa I</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(B10="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IF(C10="SI", "APROBADO", IF(B10="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(C10="SI", "🟢 Aprobada", IF(B10="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -845,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -860,7 +887,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E11" s="10">
@@ -884,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -899,7 +926,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E12" s="10">
@@ -923,7 +950,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario I</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -938,7 +965,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E13" s="10">
@@ -960,49 +987,49 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Práctica Docente II</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>5. El panel lateral calcula tu avance y porcentaje de carrera en vivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Lengua Francesa II</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>2° Año</t>
         </is>
       </c>
-      <c r="E14" s="10">
-        <f>IF(B14="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
-        <f>IF(C14="SI", "APROBADO", IF(B14="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="11">
-        <f>IF(C14="SI", "🟢 Aprobada", IF(B14="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>5. El panel lateral calcula tu avance y porcentaje de carrera en vivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+      <c r="E15" s="10">
+        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1013,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Fonética y Fonología Francesa II</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1028,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1047,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Residencia I</t>
+          <t>Gramática Francesa II</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1062,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1081,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Espacio de Definición Institucional</t>
+          <t>Literatura Francesa I (Siglos XVI al XVIII)</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1096,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1115,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente III</t>
+          <t>Civilización y Cultura Francesa II</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1130,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1146,17 +1173,44 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica General</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(B20="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(C20="SI", "APROBADO", IF(B20="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF(C20="SI", "🟢 Aprobada", IF(B20="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Residencia II / Taller de Cierre</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1171,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1190,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Sujetos de la Educación</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1205,7 +1259,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E22" s="10">
@@ -1224,7 +1278,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Investigación Educativa</t>
+          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario II y Residencia</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1239,7 +1293,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1255,51 +1309,51 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Práctica Docente IV</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E24" s="10">
-        <f>IF(B24="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F24" s="10">
-        <f>IF(C24="SI", "APROBADO", IF(B24="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G24" s="11">
-        <f>IF(C24="SI", "🟢 Aprobada", IF(B24="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Lengua Francesa III</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior I</t>
+          <t>Lingüística Aplicada al Francés</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1314,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1333,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Aplicada</t>
+          <t>Literatura Francesa II (Siglo XIX)</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1348,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1367,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Superior</t>
+          <t>Didáctica Especial y Construcción de la Práctica Docente en Nivel Medio I</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1401,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior I</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1416,7 +1470,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1432,51 +1486,51 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Especialización Superior II</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E31" s="10">
-        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G31" s="11">
-        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Derechos Humanos, Sociedad y Estado</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E30" s="10">
+        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
+          <t>Lengua Francesa IV</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1491,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1510,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior II</t>
+          <t>Literatura Francesa y Francófona Contemporánea (Siglo XX y XXI)</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1525,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1544,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Acreditación de Residencia Superior</t>
+          <t>Estudios Francófonos y Diversidad Cultural</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1559,7 +1613,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1575,27 +1629,237 @@
         <v/>
       </c>
     </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica Especial y Residencia en Nivel Medio y Superior</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Educación Sexual Integral (ESI)</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E36" s="10">
+        <f>IF(B36="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>IF(C36="SI", "APROBADO", IF(B36="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G36" s="11">
+        <f>IF(C36="SI", "🟢 Aprobada", IF(B36="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Ética y Trabajo Docente</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E37" s="10">
+        <f>IF(B37="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F37" s="10">
+        <f>IF(C37="SI", "APROBADO", IF(B37="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G37" s="11">
+        <f>IF(C37="SI", "🟢 Aprobada", IF(B37="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Seminario de Literatura y Cine Francófono</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E39" s="10">
+        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
+        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Seminario de Lingüística y Didáctica del FLE</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E40" s="10">
+        <f>IF(B40="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F40" s="10">
+        <f>IF(C40="SI", "APROBADO", IF(B40="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="11">
+        <f>IF(C40="SI", "🟢 Aprobada", IF(B40="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Taller de Traducción Francés-Español</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E41" s="10">
+        <f>IF(B41="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F41" s="10">
+        <f>IF(C41="SI", "APROBADO", IF(B41="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="11">
+        <f>IF(C41="SI", "🟢 Aprobada", IF(B41="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="I14:J14"/>
+  <mergeCells count="15">
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B11 B12 B13 B14 B16 B17 B18 B19 B21 B22 B23 B24 B26 B27 B28 B29 B31 B32 B33 B34 C6 C7 C8 C9 C11 C12 C13 C14 C16 C17 C18 C19 C21 C22 C23 C24 C26 C27 C28 C29 C31 C32 C33 C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B15 B16 B17 B18 B19 B20 B21 B22 B23 B25 B26 B27 B28 B29 B30 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C13 C15 C16 C17 C18 C19 C20 C21 C22 C23 C25 C26 C27 C28 C29 C30 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Frances.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Frances.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B41, "SI")</f>
+        <f>COUNTIF(B6:B53, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C41, "SI")</f>
+        <f>COUNTIF(C6:C53, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F53, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Lengua Francesa I</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B41, "SI")/32</f>
+        <f>COUNTIF(B6:B53, "SI")/44</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Fonética y Fonología Francesa I</t>
+          <t>Lengua francesa 1</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C41, "SI")/32</f>
+        <f>COUNTIF(C6:C53, "SI")/44</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Gramática Francesa I</t>
+          <t>Introducción a los estudios socioculturales</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Laboratorio y Expresión Oral I</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Civilización y Cultura Francesa I</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Taller de oralidad en frances</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Fonética y fonología 1</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -950,7 +950,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario I</t>
+          <t>Gramática 1</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -987,10 +987,37 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Sujetos del nivel</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E14" s="10">
+        <f>IF(B14="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F14" s="10">
+        <f>IF(C14="SI", "APROBADO", IF(B14="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>IF(C14="SI", "🟢 Aprobada", IF(B14="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Lengua Francesa II</t>
+          <t>Psicología educacional</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1037,44 +1064,17 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Fonética y Fonología Francesa II</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E16" s="10">
-        <f>IF(B16="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
-        <f>IF(C16="SI", "APROBADO", IF(B16="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
-        <f>IF(C16="SI", "🟢 Aprobada", IF(B16="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Gramática Francesa II</t>
+          <t>Nuevas tecnologias</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Literatura Francesa I (Siglos XVI al XVIII)</t>
+          <t>DDHH, sociedad y estado</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Civilización y Cultura Francesa II</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Lengua francesa 2</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Gramática 2</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Introducción a la literatura</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario II y Residencia</t>
+          <t>Fonética y fonología 2</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1309,17 +1309,44 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Historia de Francia 1</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E24" s="10">
+        <f>IF(B24="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F24" s="10">
+        <f>IF(C24="SI", "APROBADO", IF(B24="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G24" s="11">
+        <f>IF(C24="SI", "🟢 Aprobada", IF(B24="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Lengua Francesa III</t>
+          <t>Didáctica general</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1334,7 +1361,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1353,7 +1380,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Lingüística Aplicada al Francés</t>
+          <t>Lengua Extranjera 1</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1368,7 +1395,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1387,7 +1414,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Literatura Francesa II (Siglo XIX)</t>
+          <t>Lengua Extranjera 2</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1402,7 +1429,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1418,44 +1445,17 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Didáctica Especial y Construcción de la Práctica Docente en Nivel Medio I</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E28" s="10">
-        <f>IF(B28="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F28" s="10">
-        <f>IF(C28="SI", "APROBADO", IF(B28="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G28" s="11">
-        <f>IF(C28="SI", "🟢 Aprobada", IF(B28="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Historia de Francia 2</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Fonética y fonología 3</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1520,17 +1520,44 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Esi</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E31" s="10">
+        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
+        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Lengua Francesa IV</t>
+          <t>Didáctica para el nivel incial y primario / Construcción de la práctica docente</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1564,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Literatura Francesa y Francófona Contemporánea (Siglo XX y XXI)</t>
+          <t>Lengua francesa 3</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1625,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Estudios Francófonos y Diversidad Cultural</t>
+          <t>Linguistica general y análisis del discurso</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1640,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1632,7 +1659,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Didáctica Especial y Residencia en Nivel Medio y Superior</t>
+          <t>Literatura francesa 1</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1647,7 +1674,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1666,7 +1693,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Didactica para nivel medio 1 y construcción de la práctica docente</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1681,7 +1708,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1697,51 +1724,51 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Ética y Trabajo Docente</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica de la fonética</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>4° Año</t>
         </is>
       </c>
-      <c r="E37" s="10">
-        <f>IF(B37="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F37" s="10">
-        <f>IF(C37="SI", "APROBADO", IF(B37="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G37" s="11">
-        <f>IF(C37="SI", "🟢 Aprobada", IF(B37="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+      <c r="E38" s="10">
+        <f>IF(B38="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F38" s="10">
+        <f>IF(C38="SI", "APROBADO", IF(B38="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="11">
+        <f>IF(C38="SI", "🟢 Aprobada", IF(B38="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Literatura y Cine Francófono</t>
+          <t>Sistema y política educativa</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1756,7 +1783,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1775,7 +1802,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Lingüística y Didáctica del FLE</t>
+          <t>Residencia para el nivel inicial y primario</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1790,7 +1817,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1809,7 +1836,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Taller de Traducción Francés-Español</t>
+          <t>Literatura francesa 2</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1824,7 +1851,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1840,26 +1867,407 @@
         <v/>
       </c>
     </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Gramática del texto</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E42" s="10">
+        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F42" s="10">
+        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
+        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Lengua francesa 4</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E43" s="10">
+        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica del FLE para el nivel medio 2 y residencia</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E44" s="10">
+        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F44" s="10">
+        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la Educación Argentina</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Introducción a la investigación en ciencias del lenguaje</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Literatura francesa contemporánea</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Estudios linguísticos comparados</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la lengua francesa</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E50" s="10">
+        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="11">
+        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Historia del Arte</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E51" s="10">
+        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="11">
+        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E52" s="10">
+        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F52" s="10">
+        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="11">
+        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Didactica del FLE para nivel superior y residencia</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E53" s="10">
+        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F53" s="10">
+        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="11">
+        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B15 B16 B17 B18 B19 B20 B21 B22 B23 B25 B26 B27 B28 B29 B30 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C13 C15 C16 C17 C18 C19 C20 C21 C22 C23 C25 C26 C27 C28 C29 C30 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B29 B30 B31 B32 B33 B34 B35 B36 B38 B39 B40 B41 B42 B43 B44 B46 B47 B48 B49 B50 B51 B52 B53 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C29 C30 C31 C32 C33 C34 C35 C36 C38 C39 C40 C41 C42 C43 C44 C46 C47 C48 C49 C50 C51 C52 C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
